--- a/config/chip/libs.xlsx
+++ b/config/chip/libs.xlsx
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>物防・特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>物防・特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -17135,7 +17135,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -18659,7 +18659,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -21007,7 +21007,7 @@
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -21305,7 +21305,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>制御率</t>
+          <t>控制率</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -21573,7 +21573,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -21640,7 +21640,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>治癒効果</t>
+          <t>治疗效果</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -22129,7 +22129,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>反撃</t>
+          <t>反击</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性</t>
+          <t>伤害减免</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>覚醒値回復速度</t>
+          <t>觉醒值回复速度</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>物防·特防無視</t>
+          <t>无视物防、特防</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>会心率</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>会心ダメージ</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>ダメージ</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>スキルダメージ</t>
+          <t>技能伤害</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
